--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486953_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486953_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0674</v>
+        <v>5.4256</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6979</v>
+        <v>3.6475</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3694</v>
+        <v>1.7782</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0582</v>
+        <v>5.0171</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9949</v>
+        <v>2.3231</v>
       </c>
       <c r="I2" t="n">
-        <v>0.06320000000000001</v>
+        <v>2.694</v>
       </c>
       <c r="J2" t="n">
-        <v>2.7364</v>
+        <v>6.0924</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9076</v>
+        <v>2.5408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8288</v>
+        <v>3.5516</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.6783</v>
+        <v>-1.0753</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0873</v>
+        <v>-0.2177</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.8575</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.616</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4374</v>
+        <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4466</v>
+        <v>0.9424</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8363</v>
+        <v>0.6352</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6103</v>
+        <v>0.3072</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1786</v>
+        <v>0.6982</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9323</v>
+        <v>3.9777</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1245</v>
+        <v>2.7565</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8078</v>
+        <v>1.2212</v>
       </c>
       <c r="G3" t="n">
-        <v>5.0171</v>
+        <v>2.0582</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3231</v>
+        <v>1.9949</v>
       </c>
       <c r="I3" t="n">
-        <v>2.694</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0924</v>
+        <v>2.7364</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5408</v>
+        <v>1.9076</v>
       </c>
       <c r="L3" t="n">
-        <v>3.5516</v>
+        <v>0.8288</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0753</v>
+        <v>-0.6783</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2177</v>
+        <v>0.0873</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8575</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4491</v>
+        <v>1.357</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1122</v>
+        <v>0.8949</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3368</v>
+        <v>0.4621</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6982</v>
+        <v>1.1786</v>
       </c>
       <c r="W3" t="n">
+        <v>1.1786</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.6982</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8223</v>
+        <v>3.467</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9435</v>
+        <v>3.3923</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8788</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5544</v>
+        <v>3.3231</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1858</v>
+        <v>0.2107</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3686</v>
+        <v>3.1124</v>
       </c>
       <c r="J4" t="n">
-        <v>2.867</v>
+        <v>2.3729</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7092</v>
+        <v>0.0973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1579</v>
+        <v>2.2756</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6873</v>
+        <v>0.9502</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4766</v>
+        <v>0.1134</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2107</v>
+        <v>0.8368</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>0.616</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9661</v>
+        <v>0.3574</v>
       </c>
       <c r="T4" t="n">
-        <v>2.828</v>
+        <v>0.43</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1381</v>
+        <v>-0.0726</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8768</v>
+        <v>-0.8295</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6982</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6364</v>
+        <v>3.3605</v>
       </c>
       <c r="E5" t="n">
-        <v>1.82</v>
+        <v>1.7813</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8164</v>
+        <v>1.5792</v>
       </c>
       <c r="G5" t="n">
         <v>2.381</v>
@@ -844,13 +844,13 @@
         <v>1.2321</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9617</v>
+        <v>0.6859</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8677</v>
+        <v>0.829</v>
       </c>
       <c r="U5" t="n">
-        <v>0.094</v>
+        <v>-0.1431</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9384</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3415</v>
+        <v>2.5779</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7724</v>
+        <v>1.8309</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5691000000000001</v>
+        <v>0.7469</v>
       </c>
       <c r="G6" t="n">
         <v>-0.109</v>
@@ -922,13 +922,13 @@
         <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2184</v>
+        <v>1.4548</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0725</v>
+        <v>1.1311</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1458</v>
+        <v>0.3237</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.6319</v>
+        <v>2.2393</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7646</v>
+        <v>1.479</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1327</v>
+        <v>0.7603</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3231</v>
+        <v>3.5544</v>
       </c>
       <c r="H7" t="n">
+        <v>3.1858</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.867</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.7092</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.6873</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4766</v>
+      </c>
+      <c r="O7" t="n">
         <v>0.2107</v>
       </c>
-      <c r="I7" t="n">
-        <v>3.1124</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.3729</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0973</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2.2756</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.9502</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.1134</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.8368</v>
-      </c>
       <c r="P7" t="n">
-        <v>0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R7" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4777</v>
+        <v>1.3831</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1976</v>
+        <v>1.3636</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2801</v>
+        <v>0.0195</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8295</v>
+        <v>-1.8768</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5893</v>
+        <v>-0.6982</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6339</v>
+        <v>2.0432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1604</v>
+        <v>0.2193</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7943</v>
+        <v>1.8239</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0945</v>
@@ -1078,13 +1078,13 @@
         <v>2.6694</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0856</v>
+        <v>0.495</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1513</v>
+        <v>0.2284</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2369</v>
+        <v>0.2665</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2111</v>
+        <v>1.8906</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2393</v>
+        <v>-1.4412</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4504</v>
+        <v>3.3318</v>
       </c>
       <c r="G9" t="n">
         <v>0.6860000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0877</v>
+        <v>0.7672</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1045</v>
+        <v>0.9026</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0168</v>
+        <v>-0.1354</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9251</v>
+        <v>1.4637</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6044</v>
+        <v>-0.9768</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5295</v>
+        <v>2.4405</v>
       </c>
       <c r="G10" t="n">
         <v>0.6355</v>
@@ -1234,13 +1234,13 @@
         <v>0.8214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2546</v>
+        <v>0.7933</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3021</v>
+        <v>0.9297</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0475</v>
+        <v>-0.1364</v>
       </c>
       <c r="V10" t="n">
         <v>0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2349</v>
+        <v>0.6812</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.248</v>
+        <v>-0.0388</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4829</v>
+        <v>0.72</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4354</v>
@@ -1312,13 +1312,13 @@
         <v>1.4374</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1077</v>
+        <v>0.554</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1122</v>
+        <v>0.3214</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0046</v>
+        <v>0.2326</v>
       </c>
       <c r="V11" t="n">
         <v>1.1786</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.7929</v>
+        <v>-0.8003</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8827</v>
+        <v>-1.7123</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0898</v>
+        <v>0.912</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2714</v>
@@ -1390,13 +1390,13 @@
         <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0759</v>
+        <v>-0.0833</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1976</v>
+        <v>-0.0271</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1217</v>
+        <v>-0.0561</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2402</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9222</v>
+        <v>-2.2758</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4896</v>
+        <v>-3.1099</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5673</v>
+        <v>0.8341</v>
       </c>
       <c r="G13" t="n">
         <v>0.3291</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8489</v>
+        <v>-0.2024</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3294</v>
+        <v>0.0503</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5195</v>
+        <v>-0.2527</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3491</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.7217</v>
+        <v>24.0506</v>
       </c>
       <c r="E14" t="n">
-        <v>7.4985</v>
+        <v>7.8278</v>
       </c>
       <c r="F14" t="n">
-        <v>16.223</v>
+        <v>16.2229</v>
       </c>
       <c r="G14" t="n">
         <v>17.0741</v>
@@ -1534,7 +1534,7 @@
         <v>3.3865</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1340000000000002</v>
+        <v>0.134</v>
       </c>
       <c r="P14" t="n">
         <v>0.000100000000000211</v>
@@ -1546,13 +1546,13 @@
         <v>17.4542</v>
       </c>
       <c r="S14" t="n">
-        <v>8.174999999999999</v>
+        <v>8.5044</v>
       </c>
       <c r="T14" t="n">
-        <v>7.3596</v>
+        <v>7.6891</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8151</v>
+        <v>0.8153000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.527699999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7447</v>
+        <v>3.1328</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7308</v>
+        <v>2.2078</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0139</v>
+        <v>0.9249000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>2.8466</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.067</v>
+        <v>-0.679</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6778</v>
+        <v>0.1548</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7448</v>
+        <v>-0.8338</v>
       </c>
       <c r="V15" t="n">
         <v>0.3491</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0488</v>
+        <v>-0.3505</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5538</v>
+        <v>-0.0738</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.505</v>
+        <v>-0.2766</v>
       </c>
       <c r="G16" t="n">
         <v>-2.2421</v>
@@ -1702,13 +1702,13 @@
         <v>3.4908</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1733</v>
+        <v>-0.5725</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8559</v>
+        <v>0.2283</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0292</v>
+        <v>-0.8008</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9864</v>
+        <v>-1.772</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1383</v>
+        <v>-2.0337</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1519</v>
+        <v>0.2618</v>
       </c>
       <c r="G17" t="n">
         <v>2.1936</v>
@@ -1780,13 +1780,13 @@
         <v>2.6694</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8411</v>
+        <v>-0.6267</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4806</v>
+        <v>-0.376</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3605</v>
+        <v>-0.2507</v>
       </c>
       <c r="V17" t="n">
         <v>1.1786</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8595</v>
+        <v>-3.271</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2564</v>
+        <v>-0.5702</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.6032</v>
+        <v>-2.7008</v>
       </c>
       <c r="G18" t="n">
         <v>-3.8982</v>
@@ -1858,13 +1858,13 @@
         <v>2.2588</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.496</v>
       </c>
       <c r="T18" t="n">
-        <v>0.08500000000000001</v>
+        <v>-0.2288</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1695</v>
+        <v>-0.2672</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1088</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RODRIGUEZ SOLER</t>
+          <t>P. SUÁREZ CUSTODIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7918</v>
+        <v>-3.3297</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4378</v>
+        <v>-3.4014</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.354</v>
+        <v>0.0717</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0401</v>
+        <v>-3.0439</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-2.1282</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1575</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4622</v>
+        <v>-2.1924</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1168</v>
+        <v>-1.2974</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.579</v>
+        <v>-0.895</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.578</v>
+        <v>-0.8515</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9994</v>
+        <v>-0.8308</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5786</v>
+        <v>-0.0207</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R19" t="n">
         <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8071</v>
+        <v>-0.6964</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1045</v>
+        <v>-0.1823</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9116</v>
+        <v>-0.5142</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SUÁREZ CUSTODIO</t>
+          <t>G. RODRIGUEZ SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9137</v>
+        <v>-3.5494</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1336</v>
+        <v>-3.5424</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2199</v>
+        <v>-0.007</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0439</v>
+        <v>-2.0401</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1282</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-1.1575</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.1924</v>
+        <v>-0.4622</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2974</v>
+        <v>0.1168</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.895</v>
+        <v>-0.579</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8515</v>
+        <v>-1.578</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8308</v>
+        <v>-0.9994</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0207</v>
+        <v>-0.5786</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4107</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>-3.0801</v>
       </c>
       <c r="R20" t="n">
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2804</v>
+        <v>-0.5647</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9145</v>
+        <v>-0.0001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.366</v>
+        <v>-0.5646</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7889</v>
+        <v>-4.4616</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5394</v>
+        <v>-1.8173</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2495</v>
+        <v>-2.6443</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.697</v>
+        <v>-1.5533</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.9445</v>
+        <v>-0.4931</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-1.0602</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.3696</v>
+        <v>-0.8098</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.1719</v>
+        <v>-0.1649</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1977</v>
+        <v>-0.6449</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3275</v>
+        <v>-0.7435</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7726</v>
+        <v>-0.3281</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5548</v>
+        <v>-0.4154</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5107</v>
+        <v>-1.4073</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2245</v>
+        <v>-0.221</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.7352</v>
+        <v>-1.1863</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4189</v>
+        <v>-2.117</v>
       </c>
       <c r="W21" t="n">
-        <v>1.6591</v>
+        <v>0.2402</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0349</v>
+        <v>-4.6721</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5572</v>
+        <v>-3.7487</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4777</v>
+        <v>-0.9234</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.6397</v>
+        <v>-4.697</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2111</v>
+        <v>-3.9445</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.4286</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.038</v>
+        <v>-3.3696</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3698</v>
+        <v>-3.1719</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.4078</v>
+        <v>-0.1977</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6017</v>
+        <v>-1.3275</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.581</v>
+        <v>-0.7726</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0208</v>
+        <v>-0.5548</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8214</v>
+        <v>-0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8214</v>
+        <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3254</v>
+        <v>-1.3939</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5192</v>
+        <v>0.0153</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8062</v>
+        <v>-1.4091</v>
       </c>
       <c r="V22" t="n">
-        <v>0.1088</v>
+        <v>1.4189</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X22" t="n">
-        <v>0.1088</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1397</v>
+        <v>-4.7507</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4449</v>
+        <v>-3.2434</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.6949</v>
+        <v>-1.5073</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5533</v>
+        <v>-4.6397</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4931</v>
+        <v>-0.2111</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0602</v>
+        <v>-4.4286</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8098</v>
+        <v>-3.038</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1649</v>
+        <v>0.3698</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6449</v>
+        <v>-3.4078</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7435</v>
+        <v>-1.6017</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3281</v>
+        <v>-0.581</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4154</v>
+        <v>-1.0208</v>
       </c>
       <c r="P23" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0855</v>
+        <v>-1.0412</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8486</v>
+        <v>-0.2054</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2369</v>
+        <v>-0.8358</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.117</v>
+        <v>0.1088</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.3573</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.7214</v>
+        <v>-23.0242</v>
       </c>
       <c r="E24" t="n">
-        <v>-16.223</v>
+        <v>-16.2231</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.4986</v>
+        <v>-6.800999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-17.0741</v>
@@ -2296,22 +2296,22 @@
         <v>-10.5758</v>
       </c>
       <c r="I24" t="n">
-        <v>-6.498500000000001</v>
+        <v>-6.4985</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5203</v>
+        <v>-3.520299999999999</v>
       </c>
       <c r="K24" t="n">
         <v>-3.3863</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1340000000000006</v>
+        <v>-0.1340000000000003</v>
       </c>
       <c r="M24" t="n">
         <v>-13.5539</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.1894</v>
+        <v>-7.189399999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-6.3645</v>
@@ -2326,22 +2326,22 @@
         <v>17.454</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.175000000000001</v>
+        <v>-7.4777</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8151999999999997</v>
+        <v>-0.8152</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.359900000000001</v>
+        <v>-6.6625</v>
       </c>
       <c r="V24" t="n">
         <v>1.5278</v>
       </c>
       <c r="W24" t="n">
-        <v>5.566599999999999</v>
+        <v>5.5666</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.0388</v>
+        <v>-4.038800000000001</v>
       </c>
     </row>
   </sheetData>
